--- a/Results/Phase 2/Methanol/methanol human toxicity non-carcinogenic results.xlsx
+++ b/Results/Phase 2/Methanol/methanol human toxicity non-carcinogenic results.xlsx
@@ -3314,85 +3314,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>6.039604934415344e-09</v>
+        <v>5.521283154518017e-09</v>
       </c>
       <c r="C33" t="n">
-        <v>3.44027681770594e-09</v>
+        <v>3.29662621171604e-09</v>
       </c>
       <c r="D33" t="n">
-        <v>5.3430155843045e-09</v>
+        <v>5.082475897751945e-09</v>
       </c>
       <c r="E33" t="n">
-        <v>4.80767585690464e-09</v>
+        <v>4.645635486699814e-09</v>
       </c>
       <c r="F33" t="n">
-        <v>5.249098231836674e-09</v>
+        <v>5.024708484579381e-09</v>
       </c>
       <c r="G33" t="n">
-        <v>6.217859456446687e-09</v>
+        <v>5.623300085755904e-09</v>
       </c>
       <c r="H33" t="n">
-        <v>5.220749971787214e-09</v>
+        <v>5.006457737954191e-09</v>
       </c>
       <c r="I33" t="n">
-        <v>5.190761045285645e-09</v>
+        <v>4.992826216427835e-09</v>
       </c>
       <c r="J33" t="n">
-        <v>5.907157388101671e-09</v>
+        <v>5.427724558284381e-09</v>
       </c>
       <c r="K33" t="n">
-        <v>5.295459282750405e-09</v>
+        <v>5.055693250966195e-09</v>
       </c>
       <c r="L33" t="n">
-        <v>6.561685375004172e-09</v>
+        <v>5.81493739883412e-09</v>
       </c>
       <c r="M33" t="n">
-        <v>7.534014179142491e-09</v>
+        <v>6.348882689293846e-09</v>
       </c>
       <c r="N33" t="n">
-        <v>5.240368763516085e-09</v>
+        <v>5.025306096668348e-09</v>
       </c>
       <c r="O33" t="n">
-        <v>9.562130198126808e-09</v>
+        <v>9.24694023556496e-09</v>
       </c>
       <c r="P33" t="n">
-        <v>5.669962145907292e-09</v>
+        <v>5.294382552506591e-09</v>
       </c>
       <c r="Q33" t="n">
-        <v>5.288130250619405e-09</v>
+        <v>5.052416475856616e-09</v>
       </c>
       <c r="R33" t="n">
-        <v>5.155112555435323e-09</v>
+        <v>4.971116826609333e-09</v>
       </c>
       <c r="S33" t="n">
-        <v>5.899331627909746e-09</v>
+        <v>5.428903882999622e-09</v>
       </c>
       <c r="T33" t="n">
-        <v>5.244754182241916e-09</v>
+        <v>5.02488121030569e-09</v>
       </c>
       <c r="U33" t="n">
-        <v>6.897132380748504e-09</v>
+        <v>5.956880514152377e-09</v>
       </c>
       <c r="V33" t="n">
-        <v>5.43732514235421e-09</v>
+        <v>5.150333571333586e-09</v>
       </c>
       <c r="W33" t="n">
-        <v>5.559963619083561e-09</v>
+        <v>5.246369291214457e-09</v>
       </c>
       <c r="X33" t="n">
-        <v>5.710878686679035e-09</v>
+        <v>5.298777412693477e-09</v>
       </c>
       <c r="Y33" t="n">
-        <v>5.810436082735576e-09</v>
+        <v>5.364398282733319e-09</v>
       </c>
       <c r="Z33" t="n">
-        <v>5.122556107552514e-09</v>
+        <v>4.788182623481057e-09</v>
       </c>
       <c r="AA33" t="n">
-        <v>5.496079736936226e-09</v>
+        <v>5.178176139710751e-09</v>
       </c>
       <c r="AB33" t="n">
-        <v>8.715538799495749e-09</v>
+        <v>7.004718335765485e-09</v>
       </c>
     </row>
   </sheetData>
@@ -6286,85 +6286,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4.927136175580637e-09</v>
+        <v>4.793408738413733e-09</v>
       </c>
       <c r="C33" t="n">
-        <v>3.330090109727118e-09</v>
+        <v>3.18820078659452e-09</v>
       </c>
       <c r="D33" t="n">
-        <v>5.006964383664063e-09</v>
+        <v>4.834267821217144e-09</v>
       </c>
       <c r="E33" t="n">
-        <v>4.439367679961807e-09</v>
+        <v>4.379342124528253e-09</v>
       </c>
       <c r="F33" t="n">
-        <v>4.94981004159649e-09</v>
+        <v>4.8003933428352e-09</v>
       </c>
       <c r="G33" t="n">
-        <v>5.06397213213745e-09</v>
+        <v>4.875473776904273e-09</v>
       </c>
       <c r="H33" t="n">
-        <v>5.007281946765072e-09</v>
+        <v>4.832058294445863e-09</v>
       </c>
       <c r="I33" t="n">
-        <v>5.000215499904472e-09</v>
+        <v>4.830592231449836e-09</v>
       </c>
       <c r="J33" t="n">
-        <v>5.030166278921255e-09</v>
+        <v>4.852737511174045e-09</v>
       </c>
       <c r="K33" t="n">
-        <v>5.023716626605301e-09</v>
+        <v>4.842442554658715e-09</v>
       </c>
       <c r="L33" t="n">
-        <v>5.008699394340558e-09</v>
+        <v>4.838363815892481e-09</v>
       </c>
       <c r="M33" t="n">
-        <v>5.052656538569802e-09</v>
+        <v>4.859327647275197e-09</v>
       </c>
       <c r="N33" t="n">
-        <v>4.974302019334719e-09</v>
+        <v>4.819266450444125e-09</v>
       </c>
       <c r="O33" t="n">
-        <v>8.776242760496746e-09</v>
+        <v>8.637862783547821e-09</v>
       </c>
       <c r="P33" t="n">
-        <v>4.958633405468605e-09</v>
+        <v>4.812848949292148e-09</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.962926781458496e-09</v>
+        <v>4.811031368090936e-09</v>
       </c>
       <c r="R33" t="n">
-        <v>5.008714583521015e-09</v>
+        <v>4.8352727991939e-09</v>
       </c>
       <c r="S33" t="n">
-        <v>5.001624400660237e-09</v>
+        <v>4.837986902938082e-09</v>
       </c>
       <c r="T33" t="n">
-        <v>4.973545806949951e-09</v>
+        <v>4.816296279587222e-09</v>
       </c>
       <c r="U33" t="n">
-        <v>4.925809331941874e-09</v>
+        <v>4.724643255177855e-09</v>
       </c>
       <c r="V33" t="n">
-        <v>5.027345488266973e-09</v>
+        <v>4.852242960787547e-09</v>
       </c>
       <c r="W33" t="n">
-        <v>5.25667223515574e-09</v>
+        <v>5.024760731380907e-09</v>
       </c>
       <c r="X33" t="n">
-        <v>5.577490005534159e-09</v>
+        <v>5.178939781727814e-09</v>
       </c>
       <c r="Y33" t="n">
-        <v>5.538881460767852e-09</v>
+        <v>5.153515390932938e-09</v>
       </c>
       <c r="Z33" t="n">
-        <v>4.468635867978944e-09</v>
+        <v>4.321391693824569e-09</v>
       </c>
       <c r="AA33" t="n">
-        <v>5.119250527269514e-09</v>
+        <v>4.906142432307336e-09</v>
       </c>
       <c r="AB33" t="n">
-        <v>5.045725724106324e-09</v>
+        <v>4.854253065666063e-09</v>
       </c>
     </row>
   </sheetData>
@@ -9258,85 +9258,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>5.851395404057828e-09</v>
+        <v>5.403291782723789e-09</v>
       </c>
       <c r="C33" t="n">
-        <v>3.407564686669319e-09</v>
+        <v>3.272415724857413e-09</v>
       </c>
       <c r="D33" t="n">
-        <v>5.578398968732009e-09</v>
+        <v>5.21537243202853e-09</v>
       </c>
       <c r="E33" t="n">
-        <v>4.756141369188432e-09</v>
+        <v>4.612215363317155e-09</v>
       </c>
       <c r="F33" t="n">
-        <v>5.207023081799205e-09</v>
+        <v>4.996566483170924e-09</v>
       </c>
       <c r="G33" t="n">
-        <v>6.177341284904874e-09</v>
+        <v>5.596846626059342e-09</v>
       </c>
       <c r="H33" t="n">
-        <v>5.105687974159358e-09</v>
+        <v>4.936181375397641e-09</v>
       </c>
       <c r="I33" t="n">
-        <v>5.12810866995988e-09</v>
+        <v>4.952397185334931e-09</v>
       </c>
       <c r="J33" t="n">
-        <v>5.903734668037112e-09</v>
+        <v>5.421421562808805e-09</v>
       </c>
       <c r="K33" t="n">
-        <v>5.256209298096146e-09</v>
+        <v>5.027640519556676e-09</v>
       </c>
       <c r="L33" t="n">
-        <v>6.544253579018576e-09</v>
+        <v>5.800584219691028e-09</v>
       </c>
       <c r="M33" t="n">
-        <v>7.353039306148167e-09</v>
+        <v>6.2425027706559e-09</v>
       </c>
       <c r="N33" t="n">
-        <v>5.222106199045162e-09</v>
+        <v>5.010523572735391e-09</v>
       </c>
       <c r="O33" t="n">
-        <v>9.468392069289639e-09</v>
+        <v>9.176975130525164e-09</v>
       </c>
       <c r="P33" t="n">
-        <v>5.814467645285751e-09</v>
+        <v>5.378726838693852e-09</v>
       </c>
       <c r="Q33" t="n">
-        <v>5.253251509668557e-09</v>
+        <v>5.028023886636617e-09</v>
       </c>
       <c r="R33" t="n">
-        <v>5.112619807586951e-09</v>
+        <v>4.942466690654338e-09</v>
       </c>
       <c r="S33" t="n">
-        <v>5.892119853402612e-09</v>
+        <v>5.422294377208017e-09</v>
       </c>
       <c r="T33" t="n">
-        <v>5.23813445788334e-09</v>
+        <v>5.016809517267895e-09</v>
       </c>
       <c r="U33" t="n">
-        <v>6.665847278576706e-09</v>
+        <v>5.811088562298148e-09</v>
       </c>
       <c r="V33" t="n">
-        <v>5.259330758423383e-09</v>
+        <v>5.037451749755301e-09</v>
       </c>
       <c r="W33" t="n">
-        <v>5.481220023717231e-09</v>
+        <v>5.192438309142894e-09</v>
       </c>
       <c r="X33" t="n">
-        <v>5.776613807201905e-09</v>
+        <v>5.333878592796626e-09</v>
       </c>
       <c r="Y33" t="n">
-        <v>5.720749915246446e-09</v>
+        <v>5.308268608033584e-09</v>
       </c>
       <c r="Z33" t="n">
-        <v>4.997058667496695e-09</v>
+        <v>4.699735843916157e-09</v>
       </c>
       <c r="AA33" t="n">
-        <v>5.349016252838366e-09</v>
+        <v>5.087203858428477e-09</v>
       </c>
       <c r="AB33" t="n">
-        <v>8.600438920213489e-09</v>
+        <v>6.934026741683948e-09</v>
       </c>
     </row>
   </sheetData>
@@ -12230,85 +12230,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>5.711524581969617e-09</v>
+        <v>5.321218437557361e-09</v>
       </c>
       <c r="C33" t="n">
-        <v>3.44511811346654e-09</v>
+        <v>3.30079760620868e-09</v>
       </c>
       <c r="D33" t="n">
-        <v>5.703665353849357e-09</v>
+        <v>5.295222283533973e-09</v>
       </c>
       <c r="E33" t="n">
-        <v>4.735795733903108e-09</v>
+        <v>4.603771458681622e-09</v>
       </c>
       <c r="F33" t="n">
-        <v>5.293595933869029e-09</v>
+        <v>5.053511165938067e-09</v>
       </c>
       <c r="G33" t="n">
-        <v>6.116072047296118e-09</v>
+        <v>5.568366210911573e-09</v>
       </c>
       <c r="H33" t="n">
-        <v>5.11016223930709e-09</v>
+        <v>4.945307533023675e-09</v>
       </c>
       <c r="I33" t="n">
-        <v>5.369929597167682e-09</v>
+        <v>5.098629702815613e-09</v>
       </c>
       <c r="J33" t="n">
-        <v>5.888857554455215e-09</v>
+        <v>5.418716318467556e-09</v>
       </c>
       <c r="K33" t="n">
-        <v>5.429948453815368e-09</v>
+        <v>5.139132959911697e-09</v>
       </c>
       <c r="L33" t="n">
-        <v>6.37653185379457e-09</v>
+        <v>5.707887367342207e-09</v>
       </c>
       <c r="M33" t="n">
-        <v>7.081314035292581e-09</v>
+        <v>6.090123623317732e-09</v>
       </c>
       <c r="N33" t="n">
-        <v>5.196133721111566e-09</v>
+        <v>5.001160931905519e-09</v>
       </c>
       <c r="O33" t="n">
-        <v>9.415333763859859e-09</v>
+        <v>9.153423676753026e-09</v>
       </c>
       <c r="P33" t="n">
-        <v>5.8183449186191e-09</v>
+        <v>5.388375004332152e-09</v>
       </c>
       <c r="Q33" t="n">
-        <v>5.280826877034595e-09</v>
+        <v>5.050840984208449e-09</v>
       </c>
       <c r="R33" t="n">
-        <v>5.104074975027304e-09</v>
+        <v>4.943681787890347e-09</v>
       </c>
       <c r="S33" t="n">
-        <v>5.845200242646428e-09</v>
+        <v>5.400895110646137e-09</v>
       </c>
       <c r="T33" t="n">
-        <v>5.259848749540174e-09</v>
+        <v>5.035556728420973e-09</v>
       </c>
       <c r="U33" t="n">
-        <v>6.256164774061927e-09</v>
+        <v>5.588193292189353e-09</v>
       </c>
       <c r="V33" t="n">
-        <v>5.394912321652497e-09</v>
+        <v>5.127348141550936e-09</v>
       </c>
       <c r="W33" t="n">
-        <v>5.545259413876437e-09</v>
+        <v>5.254681194157101e-09</v>
       </c>
       <c r="X33" t="n">
-        <v>6.056243020911536e-09</v>
+        <v>5.504860926366608e-09</v>
       </c>
       <c r="Y33" t="n">
-        <v>6.365990144236078e-09</v>
+        <v>5.698027116488932e-09</v>
       </c>
       <c r="Z33" t="n">
-        <v>5.040967017549085e-09</v>
+        <v>4.745930645517283e-09</v>
       </c>
       <c r="AA33" t="n">
-        <v>5.365056150315401e-09</v>
+        <v>5.10260740193063e-09</v>
       </c>
       <c r="AB33" t="n">
-        <v>8.367710083407691e-09</v>
+        <v>6.804436551313859e-09</v>
       </c>
     </row>
   </sheetData>
@@ -15202,85 +15202,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>5.613470682701815e-09</v>
+        <v>5.268949271587986e-09</v>
       </c>
       <c r="C33" t="n">
-        <v>3.46867257457488e-09</v>
+        <v>3.319868189369488e-09</v>
       </c>
       <c r="D33" t="n">
-        <v>5.574348132513634e-09</v>
+        <v>5.22709366856243e-09</v>
       </c>
       <c r="E33" t="n">
-        <v>4.678640301281807e-09</v>
+        <v>4.569626973546234e-09</v>
       </c>
       <c r="F33" t="n">
-        <v>5.354402750242976e-09</v>
+        <v>5.094453225155539e-09</v>
       </c>
       <c r="G33" t="n">
-        <v>5.984305071264508e-09</v>
+        <v>5.497713707252928e-09</v>
       </c>
       <c r="H33" t="n">
-        <v>5.134662039847791e-09</v>
+        <v>4.964554998870193e-09</v>
       </c>
       <c r="I33" t="n">
-        <v>5.378625049679486e-09</v>
+        <v>5.108892028200281e-09</v>
       </c>
       <c r="J33" t="n">
-        <v>5.827727844270088e-09</v>
+        <v>5.390111679652083e-09</v>
       </c>
       <c r="K33" t="n">
-        <v>5.499488558472107e-09</v>
+        <v>5.186451123446515e-09</v>
       </c>
       <c r="L33" t="n">
-        <v>6.133392441973077e-09</v>
+        <v>5.575209919718692e-09</v>
       </c>
       <c r="M33" t="n">
-        <v>6.734851070276755e-09</v>
+        <v>5.908271097912563e-09</v>
       </c>
       <c r="N33" t="n">
-        <v>5.171720308415644e-09</v>
+        <v>4.991656883653211e-09</v>
       </c>
       <c r="O33" t="n">
-        <v>9.292824677289235e-09</v>
+        <v>9.07731745056536e-09</v>
       </c>
       <c r="P33" t="n">
-        <v>5.753926787015701e-09</v>
+        <v>5.357563062817377e-09</v>
       </c>
       <c r="Q33" t="n">
-        <v>5.31206841635389e-09</v>
+        <v>5.075122817107944e-09</v>
       </c>
       <c r="R33" t="n">
-        <v>5.186624501247473e-09</v>
+        <v>4.996274179321133e-09</v>
       </c>
       <c r="S33" t="n">
-        <v>5.787710699783177e-09</v>
+        <v>5.37243280373011e-09</v>
       </c>
       <c r="T33" t="n">
-        <v>5.315090988997069e-09</v>
+        <v>5.072668622602712e-09</v>
       </c>
       <c r="U33" t="n">
-        <v>6.30852047148179e-09</v>
+        <v>5.651254702750189e-09</v>
       </c>
       <c r="V33" t="n">
-        <v>5.659872568460673e-09</v>
+        <v>5.297685731273931e-09</v>
       </c>
       <c r="W33" t="n">
-        <v>5.633544475333014e-09</v>
+        <v>5.330607036784196e-09</v>
       </c>
       <c r="X33" t="n">
-        <v>6.157449182161069e-09</v>
+        <v>5.576177178935922e-09</v>
       </c>
       <c r="Y33" t="n">
-        <v>7.161287524692542e-09</v>
+        <v>6.167685600206818e-09</v>
       </c>
       <c r="Z33" t="n">
-        <v>5.037136551331415e-09</v>
+        <v>4.758808234606726e-09</v>
       </c>
       <c r="AA33" t="n">
-        <v>5.421458814207318e-09</v>
+        <v>5.140763808936214e-09</v>
       </c>
       <c r="AB33" t="n">
-        <v>8.043483807801137e-09</v>
+        <v>6.634041360929012e-09</v>
       </c>
     </row>
   </sheetData>
@@ -18174,85 +18174,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>5.004005452616935e-09</v>
+        <v>4.838869964898109e-09</v>
       </c>
       <c r="C33" t="n">
-        <v>3.279963993372595e-09</v>
+        <v>3.154258242568528e-09</v>
       </c>
       <c r="D33" t="n">
-        <v>5.028746335572194e-09</v>
+        <v>4.846852339543343e-09</v>
       </c>
       <c r="E33" t="n">
-        <v>4.457771591392379e-09</v>
+        <v>4.393817337308813e-09</v>
       </c>
       <c r="F33" t="n">
-        <v>4.945483949942583e-09</v>
+        <v>4.796029882344985e-09</v>
       </c>
       <c r="G33" t="n">
-        <v>5.22295274734552e-09</v>
+        <v>4.972763697403234e-09</v>
       </c>
       <c r="H33" t="n">
-        <v>5.072097235893991e-09</v>
+        <v>4.867866763622267e-09</v>
       </c>
       <c r="I33" t="n">
-        <v>4.955925370243915e-09</v>
+        <v>4.803635374132213e-09</v>
       </c>
       <c r="J33" t="n">
-        <v>5.152707341225831e-09</v>
+        <v>4.927172489911137e-09</v>
       </c>
       <c r="K33" t="n">
-        <v>5.040247738266715e-09</v>
+        <v>4.851318393993895e-09</v>
       </c>
       <c r="L33" t="n">
-        <v>5.314615948056824e-09</v>
+        <v>5.02609699492266e-09</v>
       </c>
       <c r="M33" t="n">
-        <v>5.621200224174072e-09</v>
+        <v>5.199670155305834e-09</v>
       </c>
       <c r="N33" t="n">
-        <v>4.999264377723658e-09</v>
+        <v>4.83197909028372e-09</v>
       </c>
       <c r="O33" t="n">
-        <v>8.778142016578744e-09</v>
+        <v>8.626724865238428e-09</v>
       </c>
       <c r="P33" t="n">
-        <v>5.098369552352044e-09</v>
+        <v>4.897973403886762e-09</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.989951873178986e-09</v>
+        <v>4.825469940825236e-09</v>
       </c>
       <c r="R33" t="n">
-        <v>4.988117815112122e-09</v>
+        <v>4.822038591885885e-09</v>
       </c>
       <c r="S33" t="n">
-        <v>5.080982867764425e-09</v>
+        <v>4.885505727267783e-09</v>
       </c>
       <c r="T33" t="n">
-        <v>4.969023743399454e-09</v>
+        <v>4.809409805355449e-09</v>
       </c>
       <c r="U33" t="n">
-        <v>5.279451534096018e-09</v>
+        <v>4.914847666408669e-09</v>
       </c>
       <c r="V33" t="n">
-        <v>4.969910120062758e-09</v>
+        <v>4.814654850412079e-09</v>
       </c>
       <c r="W33" t="n">
-        <v>5.208797917719321e-09</v>
+        <v>4.965753034137885e-09</v>
       </c>
       <c r="X33" t="n">
-        <v>5.138609785886456e-09</v>
+        <v>4.912439842207583e-09</v>
       </c>
       <c r="Y33" t="n">
-        <v>5.006662219173651e-09</v>
+        <v>4.836271199100827e-09</v>
       </c>
       <c r="Z33" t="n">
-        <v>4.561732037272915e-09</v>
+        <v>4.37376209013017e-09</v>
       </c>
       <c r="AA33" t="n">
-        <v>5.061018934242608e-09</v>
+        <v>4.86954611362195e-09</v>
       </c>
       <c r="AB33" t="n">
-        <v>5.70212350774139e-09</v>
+        <v>5.233867184391989e-09</v>
       </c>
     </row>
   </sheetData>
@@ -21146,85 +21146,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4.924586892267001e-09</v>
+        <v>4.787273783728694e-09</v>
       </c>
       <c r="C33" t="n">
-        <v>3.315230673777069e-09</v>
+        <v>3.172971436601309e-09</v>
       </c>
       <c r="D33" t="n">
-        <v>4.977896182155707e-09</v>
+        <v>4.810713135802714e-09</v>
       </c>
       <c r="E33" t="n">
-        <v>4.447615000923182e-09</v>
+        <v>4.384105372571478e-09</v>
       </c>
       <c r="F33" t="n">
-        <v>4.951834955699799e-09</v>
+        <v>4.795868629724497e-09</v>
       </c>
       <c r="G33" t="n">
-        <v>5.026312537746417e-09</v>
+        <v>4.844846689777162e-09</v>
       </c>
       <c r="H33" t="n">
-        <v>5.013307897530808e-09</v>
+        <v>4.829887285921008e-09</v>
       </c>
       <c r="I33" t="n">
-        <v>4.991895167893033e-09</v>
+        <v>4.819749989276369e-09</v>
       </c>
       <c r="J33" t="n">
-        <v>5.00490353053414e-09</v>
+        <v>4.83136638061447e-09</v>
       </c>
       <c r="K33" t="n">
-        <v>5.001783985926638e-09</v>
+        <v>4.823798412146731e-09</v>
       </c>
       <c r="L33" t="n">
-        <v>4.98983860747785e-09</v>
+        <v>4.81629814546567e-09</v>
       </c>
       <c r="M33" t="n">
-        <v>4.996911608595919e-09</v>
+        <v>4.816163357065339e-09</v>
       </c>
       <c r="N33" t="n">
-        <v>4.996848680395609e-09</v>
+        <v>4.827070939301365e-09</v>
       </c>
       <c r="O33" t="n">
-        <v>8.815490462136075e-09</v>
+        <v>8.65198554217746e-09</v>
       </c>
       <c r="P33" t="n">
-        <v>4.930775929138366e-09</v>
+        <v>4.791473000598172e-09</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.937549420638311e-09</v>
+        <v>4.789224699312403e-09</v>
       </c>
       <c r="R33" t="n">
-        <v>5.00340830695222e-09</v>
+        <v>4.825921382215395e-09</v>
       </c>
       <c r="S33" t="n">
-        <v>4.980363117268275e-09</v>
+        <v>4.818578128112839e-09</v>
       </c>
       <c r="T33" t="n">
-        <v>4.938764859649036e-09</v>
+        <v>4.786629338920252e-09</v>
       </c>
       <c r="U33" t="n">
-        <v>4.763549414034457e-09</v>
+        <v>4.600450568753502e-09</v>
       </c>
       <c r="V33" t="n">
-        <v>4.994211473149078e-09</v>
+        <v>4.825629934906991e-09</v>
       </c>
       <c r="W33" t="n">
-        <v>5.123622977627501e-09</v>
+        <v>4.92062998101874e-09</v>
       </c>
       <c r="X33" t="n">
-        <v>5.385246459813491e-09</v>
+        <v>5.058891428363954e-09</v>
       </c>
       <c r="Y33" t="n">
-        <v>5.190249149090136e-09</v>
+        <v>4.942234212304628e-09</v>
       </c>
       <c r="Z33" t="n">
-        <v>4.517478601581615e-09</v>
+        <v>4.347706535285615e-09</v>
       </c>
       <c r="AA33" t="n">
-        <v>5.057036848557525e-09</v>
+        <v>4.863618618175288e-09</v>
       </c>
       <c r="AB33" t="n">
-        <v>4.960284084935859e-09</v>
+        <v>4.798557146855753e-09</v>
       </c>
     </row>
   </sheetData>
@@ -24118,85 +24118,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4.961697157183694e-09</v>
+        <v>4.814567979061535e-09</v>
       </c>
       <c r="C33" t="n">
-        <v>3.327988803539546e-09</v>
+        <v>3.187646979021916e-09</v>
       </c>
       <c r="D33" t="n">
-        <v>5.006745790090741e-09</v>
+        <v>4.833976133917634e-09</v>
       </c>
       <c r="E33" t="n">
-        <v>4.5068632990986e-09</v>
+        <v>4.421539616026059e-09</v>
       </c>
       <c r="F33" t="n">
-        <v>4.9556626523477e-09</v>
+        <v>4.803647465337686e-09</v>
       </c>
       <c r="G33" t="n">
-        <v>5.076786553079486e-09</v>
+        <v>4.883020747967433e-09</v>
       </c>
       <c r="H33" t="n">
-        <v>5.007971875608571e-09</v>
+        <v>4.83172815626536e-09</v>
       </c>
       <c r="I33" t="n">
-        <v>5.002335320768432e-09</v>
+        <v>4.831555856582809e-09</v>
       </c>
       <c r="J33" t="n">
-        <v>5.02845581355387e-09</v>
+        <v>4.851284390578921e-09</v>
       </c>
       <c r="K33" t="n">
-        <v>5.019161926613632e-09</v>
+        <v>4.840977624367531e-09</v>
       </c>
       <c r="L33" t="n">
-        <v>4.994481541315259e-09</v>
+        <v>4.826848356387424e-09</v>
       </c>
       <c r="M33" t="n">
-        <v>5.020460555044938e-09</v>
+        <v>4.838977063828499e-09</v>
       </c>
       <c r="N33" t="n">
-        <v>4.980343884922396e-09</v>
+        <v>4.822263458632055e-09</v>
       </c>
       <c r="O33" t="n">
-        <v>8.861618616337417e-09</v>
+        <v>8.695404638629347e-09</v>
       </c>
       <c r="P33" t="n">
-        <v>4.965959250871581e-09</v>
+        <v>4.816969457120305e-09</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.952748683601678e-09</v>
+        <v>4.804379518719512e-09</v>
       </c>
       <c r="R33" t="n">
-        <v>5.043587112509061e-09</v>
+        <v>4.854957783584481e-09</v>
       </c>
       <c r="S33" t="n">
-        <v>4.967614479310706e-09</v>
+        <v>4.816414284797318e-09</v>
       </c>
       <c r="T33" t="n">
-        <v>4.960164725133043e-09</v>
+        <v>4.806500024623621e-09</v>
       </c>
       <c r="U33" t="n">
-        <v>4.802086842786621e-09</v>
+        <v>4.643370912931811e-09</v>
       </c>
       <c r="V33" t="n">
-        <v>5.026289050694145e-09</v>
+        <v>4.851382099421862e-09</v>
       </c>
       <c r="W33" t="n">
-        <v>5.279608746943872e-09</v>
+        <v>5.035416511075379e-09</v>
       </c>
       <c r="X33" t="n">
-        <v>5.518763442986257e-09</v>
+        <v>5.146044114785749e-09</v>
       </c>
       <c r="Y33" t="n">
-        <v>5.207658442439982e-09</v>
+        <v>4.95750257014126e-09</v>
       </c>
       <c r="Z33" t="n">
-        <v>4.495623062133754e-09</v>
+        <v>4.339418415901774e-09</v>
       </c>
       <c r="AA33" t="n">
-        <v>5.102743012679361e-09</v>
+        <v>4.895895126681974e-09</v>
       </c>
       <c r="AB33" t="n">
-        <v>5.00995666705801e-09</v>
+        <v>4.833161767226389e-09</v>
       </c>
     </row>
   </sheetData>
@@ -27090,85 +27090,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>5.458810047699521e-09</v>
+        <v>5.15229320680093e-09</v>
       </c>
       <c r="C33" t="n">
-        <v>3.377604642636174e-09</v>
+        <v>3.244180444672592e-09</v>
       </c>
       <c r="D33" t="n">
-        <v>5.274553703560087e-09</v>
+        <v>5.02711162993546e-09</v>
       </c>
       <c r="E33" t="n">
-        <v>4.673677995535022e-09</v>
+        <v>4.553771663659089e-09</v>
       </c>
       <c r="F33" t="n">
-        <v>5.109702132573314e-09</v>
+        <v>4.928484626195775e-09</v>
       </c>
       <c r="G33" t="n">
-        <v>6.082141188955059e-09</v>
+        <v>5.536622746948039e-09</v>
       </c>
       <c r="H33" t="n">
-        <v>5.086072657179152e-09</v>
+        <v>4.9132156671503e-09</v>
       </c>
       <c r="I33" t="n">
-        <v>5.097658104542407e-09</v>
+        <v>4.922716008246328e-09</v>
       </c>
       <c r="J33" t="n">
-        <v>5.747806289118539e-09</v>
+        <v>5.323509566858633e-09</v>
       </c>
       <c r="K33" t="n">
-        <v>5.174616707454194e-09</v>
+        <v>4.966784828900824e-09</v>
       </c>
       <c r="L33" t="n">
-        <v>6.312313101080705e-09</v>
+        <v>5.660396970822729e-09</v>
       </c>
       <c r="M33" t="n">
-        <v>7.171302706586956e-09</v>
+        <v>6.162096527129213e-09</v>
       </c>
       <c r="N33" t="n">
-        <v>5.198063517689398e-09</v>
+        <v>4.985167697979268e-09</v>
       </c>
       <c r="O33" t="n">
-        <v>9.13555612086747e-09</v>
+        <v>8.925777857080156e-09</v>
       </c>
       <c r="P33" t="n">
-        <v>5.581802827169643e-09</v>
+        <v>5.226570452614068e-09</v>
       </c>
       <c r="Q33" t="n">
-        <v>5.178224212650366e-09</v>
+        <v>4.972973549819491e-09</v>
       </c>
       <c r="R33" t="n">
-        <v>5.113944809475176e-09</v>
+        <v>4.931661747996519e-09</v>
       </c>
       <c r="S33" t="n">
-        <v>5.500426240118923e-09</v>
+        <v>5.179023858054871e-09</v>
       </c>
       <c r="T33" t="n">
-        <v>5.14055693019623e-09</v>
+        <v>4.948543136557725e-09</v>
       </c>
       <c r="U33" t="n">
-        <v>6.196596948389718e-09</v>
+        <v>5.508634472312348e-09</v>
       </c>
       <c r="V33" t="n">
-        <v>5.167283445871543e-09</v>
+        <v>4.969999888938107e-09</v>
       </c>
       <c r="W33" t="n">
-        <v>5.365229834555541e-09</v>
+        <v>5.101062831786921e-09</v>
       </c>
       <c r="X33" t="n">
-        <v>5.7355971021681e-09</v>
+        <v>5.298670780967404e-09</v>
       </c>
       <c r="Y33" t="n">
-        <v>5.65311173775946e-09</v>
+        <v>5.257229403968722e-09</v>
       </c>
       <c r="Z33" t="n">
-        <v>4.856304150344252e-09</v>
+        <v>4.595709853679893e-09</v>
       </c>
       <c r="AA33" t="n">
-        <v>5.268059154516382e-09</v>
+        <v>5.02804607872716e-09</v>
       </c>
       <c r="AB33" t="n">
-        <v>8.08066487144825e-09</v>
+        <v>6.627808494722388e-09</v>
       </c>
     </row>
   </sheetData>
@@ -30062,85 +30062,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4.961785664828213e-09</v>
+        <v>4.828972513446104e-09</v>
       </c>
       <c r="C33" t="n">
-        <v>3.377748276541579e-09</v>
+        <v>3.230497964230721e-09</v>
       </c>
       <c r="D33" t="n">
-        <v>5.056302949295246e-09</v>
+        <v>4.87884272493801e-09</v>
       </c>
       <c r="E33" t="n">
-        <v>4.490668382906048e-09</v>
+        <v>4.427345667625109e-09</v>
       </c>
       <c r="F33" t="n">
-        <v>4.97032299250177e-09</v>
+        <v>4.826870533566079e-09</v>
       </c>
       <c r="G33" t="n">
-        <v>5.792969769209163e-09</v>
+        <v>5.345592425959132e-09</v>
       </c>
       <c r="H33" t="n">
-        <v>5.012746864579927e-09</v>
+        <v>4.851370925141322e-09</v>
       </c>
       <c r="I33" t="n">
-        <v>5.027021998546657e-09</v>
+        <v>4.861954733239946e-09</v>
       </c>
       <c r="J33" t="n">
-        <v>5.308568926067463e-09</v>
+        <v>5.039675129881755e-09</v>
       </c>
       <c r="K33" t="n">
-        <v>5.084233671500808e-09</v>
+        <v>4.892777660118312e-09</v>
       </c>
       <c r="L33" t="n">
-        <v>5.395099178601986e-09</v>
+        <v>5.090374267256738e-09</v>
       </c>
       <c r="M33" t="n">
-        <v>5.204226929555532e-09</v>
+        <v>4.963231153189941e-09</v>
       </c>
       <c r="N33" t="n">
-        <v>5.049268933610604e-09</v>
+        <v>4.878012344330892e-09</v>
       </c>
       <c r="O33" t="n">
-        <v>8.8677334297359e-09</v>
+        <v>8.718854066790695e-09</v>
       </c>
       <c r="P33" t="n">
-        <v>5.220345336338798e-09</v>
+        <v>4.988306259352507e-09</v>
       </c>
       <c r="Q33" t="n">
-        <v>5.019499015442336e-09</v>
+        <v>4.858769139433341e-09</v>
       </c>
       <c r="R33" t="n">
-        <v>5.044401511769795e-09</v>
+        <v>4.87126923027997e-09</v>
       </c>
       <c r="S33" t="n">
-        <v>5.05618140391116e-09</v>
+        <v>4.884840081176019e-09</v>
       </c>
       <c r="T33" t="n">
-        <v>5.00483650669297e-09</v>
+        <v>4.849034920028674e-09</v>
       </c>
       <c r="U33" t="n">
-        <v>4.982286507939907e-09</v>
+        <v>4.762565279601575e-09</v>
       </c>
       <c r="V33" t="n">
-        <v>5.029137140107495e-09</v>
+        <v>4.86596311864599e-09</v>
       </c>
       <c r="W33" t="n">
-        <v>5.210472113110025e-09</v>
+        <v>5.000121989647129e-09</v>
       </c>
       <c r="X33" t="n">
-        <v>5.568811644367322e-09</v>
+        <v>5.184865105704879e-09</v>
       </c>
       <c r="Y33" t="n">
-        <v>6.071817930774657e-09</v>
+        <v>5.487575853083793e-09</v>
       </c>
       <c r="Z33" t="n">
-        <v>4.521096092762585e-09</v>
+        <v>4.360796833476147e-09</v>
       </c>
       <c r="AA33" t="n">
-        <v>5.079689658163687e-09</v>
+        <v>4.897034639242449e-09</v>
       </c>
       <c r="AB33" t="n">
-        <v>6.711977436410135e-09</v>
+        <v>5.832636142478588e-09</v>
       </c>
     </row>
   </sheetData>
